--- a/Config/Datas/Tables/b_Boss遭遇_BossEncounterConfig.xlsx
+++ b/Config/Datas/Tables/b_Boss遭遇_BossEncounterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbBossEncounter" sheetId="1" r:id="R8da24cb0d5f14c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbBossEncounter" sheetId="1" r:id="Rf0d96bf18865462f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,7 +418,7 @@
         <x:v>monsterId</x:v>
       </x:c>
       <x:c r="D1" s="8" t="str">
-        <x:v>spawnRadiusPixelsMilli</x:v>
+        <x:v>spawnRadiusPixels</x:v>
       </x:c>
       <x:c r="E1" s="8" t="str">
         <x:v>healthBarText</x:v>
@@ -438,7 +438,7 @@
         <x:v>int#ref=TbMonster</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>int</x:v>
+        <x:v>float</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
         <x:v>string</x:v>
@@ -468,7 +468,7 @@
         <x:v>Boss怪物ID</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>相对玩家生成半径，逻辑像素乘1000</x:v>
+        <x:v>相对玩家生成半径，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
         <x:v>Boss血条名称</x:v>
@@ -486,7 +486,7 @@
         <x:v>10032</x:v>
       </x:c>
       <x:c r="D5" s="6" t="n">
-        <x:v>1000000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>btm311</x:v>
